--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -9,83 +9,91 @@
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>
   <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
     <t xml:space="preserve">판다다</t>
   </si>
   <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
     <t xml:space="preserve">곰이다</t>
   </si>
   <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
   </si>
   <si>
     <t xml:space="preserve">놀이다.</t>
@@ -94,67 +102,58 @@
     <t xml:space="preserve">도적이다.</t>
   </si>
   <si>
-    <t xml:space="preserve">상어다 </t>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
   </si>
   <si>
     <t xml:space="preserve">해골 병사다.</t>
   </si>
   <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
     <t xml:space="preserve">미노타우로스다</t>
   </si>
   <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
   </si>
   <si>
     <t xml:space="preserve">Skull</t>
   </si>
   <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
     <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
   </si>
   <si>
     <t xml:space="preserve">난쟁이다</t>
@@ -689,46 +688,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -736,10 +735,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -769,10 +768,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -780,10 +779,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1">
         <v>25</v>
@@ -813,10 +812,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -824,10 +823,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1">
         <v>40</v>
@@ -857,10 +856,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -868,10 +867,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -901,10 +900,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -912,10 +911,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1">
         <v>35</v>
@@ -945,10 +944,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -956,7 +955,7 @@
         <v>10006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>49</v>
@@ -989,10 +988,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1000,7 +999,7 @@
         <v>10007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>0</v>
@@ -1033,10 +1032,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1044,10 +1043,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1">
         <v>50</v>
@@ -1077,10 +1076,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1088,10 +1087,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1">
         <v>80</v>
@@ -1121,10 +1120,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1135,7 +1134,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1">
         <v>130</v>
@@ -1165,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>48</v>
@@ -1176,7 +1175,7 @@
         <v>10011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>47</v>
@@ -1209,10 +1208,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1220,10 +1219,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1">
         <v>40</v>
@@ -1253,10 +1252,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1264,10 +1263,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D14" s="1">
         <v>160</v>
@@ -1297,10 +1296,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1308,13 +1307,13 @@
         <v>10014</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
@@ -1341,10 +1340,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1352,10 +1351,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1">
         <v>60</v>
@@ -1385,10 +1384,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1396,10 +1395,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -1429,10 +1428,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -1440,10 +1439,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D22" s="1">
         <v>500</v>
@@ -1473,10 +1472,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O22" s="1"/>
     </row>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="50">
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -9,148 +9,147 @@
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
   <si>
     <t xml:space="preserve">뱀이다</t>
   </si>
   <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
   </si>
   <si>
     <t xml:space="preserve">move_speed</t>
   </si>
   <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hammershark</t>
   </si>
   <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
   </si>
   <si>
     <t xml:space="preserve">놀이다.</t>
   </si>
   <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
     <t xml:space="preserve">도적이다.</t>
   </si>
   <si>
-    <t xml:space="preserve">상어다 </t>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
   </si>
   <si>
     <t xml:space="preserve">해골 병사다.</t>
   </si>
   <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thief</t>
   </si>
   <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">max_hp</t>
   </si>
   <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
     <t xml:space="preserve">해골 왕이당.</t>
   </si>
   <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lizard</t>
   </si>
   <si>
@@ -160,10 +159,10 @@
     <t xml:space="preserve">난쟁이다</t>
   </si>
   <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
   </si>
 </sst>
 </file>
@@ -689,46 +688,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -736,10 +735,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -769,10 +768,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -780,10 +779,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1">
         <v>25</v>
@@ -813,10 +812,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -824,10 +823,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1">
         <v>40</v>
@@ -857,10 +856,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -868,10 +867,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -901,10 +900,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -912,10 +911,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1">
         <v>35</v>
@@ -945,10 +944,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -956,10 +955,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
@@ -989,10 +988,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1000,10 +999,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1">
         <v>20</v>
@@ -1033,10 +1032,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1044,10 +1043,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1">
         <v>50</v>
@@ -1077,10 +1076,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1121,7 +1120,7 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>45</v>
@@ -1132,10 +1131,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1">
         <v>130</v>
@@ -1165,10 +1164,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1176,7 +1175,7 @@
         <v>10011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>47</v>
@@ -1209,10 +1208,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1220,10 +1219,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1">
         <v>40</v>
@@ -1253,10 +1252,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1264,10 +1263,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1">
         <v>160</v>
@@ -1297,10 +1296,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1308,13 +1307,13 @@
         <v>10014</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D15" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
@@ -1341,10 +1340,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1352,10 +1351,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1">
         <v>60</v>
@@ -1385,10 +1384,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1396,10 +1395,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -1429,10 +1428,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -1440,10 +1439,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D22" s="1">
         <v>500</v>
@@ -1473,10 +1472,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O22" s="1"/>
     </row>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="50">
   <si>
     <t xml:space="preserve">GoblinSorcerer</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="50">
   <si>
     <t xml:space="preserve">GoblinSorcerer</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -1,170 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
-  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
+    <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -209,7 +57,7 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -234,69 +82,11 @@
       </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -381,6 +171,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -667,9 +525,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="15.5" customWidth="1"/>
@@ -686,59 +547,107 @@
     <col min="14" max="14" width="13.35546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <v>monster_name</v>
+        <is>
+          <t xml:space="preserve">monster_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <v>max_hp</v>
+        <is>
+          <t xml:space="preserve">max_hp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <v>damage</v>
+        <is>
+          <t xml:space="preserve">damage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <v>move_speed</v>
+        <is>
+          <t xml:space="preserve">move_speed</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <v>attack_delay</v>
+        <is>
+          <t xml:space="preserve">attack_delay</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <v>drop_exp_min</v>
+        <is>
+          <t xml:space="preserve">drop_exp_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <v>drop_exp_max</v>
+        <is>
+          <t xml:space="preserve">drop_exp_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <v>drop_money_min</v>
+        <is>
+          <t xml:space="preserve">drop_money_min</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <v>drop_money_max</v>
+        <is>
+          <t xml:space="preserve">drop_money_max</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <v>attack_range</v>
+        <is>
+          <t xml:space="preserve">attack_range</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <v>attack_type</v>
+        <is>
+          <t xml:space="preserve">attack_type</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <v>prefab_id</v>
+        <is>
+          <t xml:space="preserve">prefab_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1">
         <v>10001</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>39</v>
+      <c r="B2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10001_Name</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10001_Desc</t>
+        </is>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -767,22 +676,34 @@
       <c r="L2" s="1">
         <v>2</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="M2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Skull</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1">
         <v>10002</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>32</v>
+      <c r="B3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10002_Name</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10002_Desc</t>
+        </is>
       </c>
       <c r="D3" s="1">
         <v>25</v>
@@ -794,7 +715,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>0.69999999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="H3" s="1">
         <v>30</v>
@@ -811,22 +732,34 @@
       <c r="L3" s="1">
         <v>1.5</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="M3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Thief</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="1">
         <v>10003</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
+      <c r="B4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10003_Name</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10003_Desc</t>
+        </is>
       </c>
       <c r="D4" s="1">
         <v>40</v>
@@ -838,7 +771,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>2.7000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="H4" s="1">
         <v>40</v>
@@ -855,22 +788,34 @@
       <c r="L4" s="1">
         <v>6</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="M4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Ranged</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Gnoll</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="1">
         <v>10004</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>42</v>
+      <c r="B5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10004_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10004_Desc</t>
+        </is>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -899,22 +844,34 @@
       <c r="L5" s="1">
         <v>2</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="M5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Hammershark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="1">
         <v>10005</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
+      <c r="B6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10005_Name</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10005_Desc</t>
+        </is>
       </c>
       <c r="D6" s="1">
         <v>35</v>
@@ -943,22 +900,34 @@
       <c r="L6" s="1">
         <v>5</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="M6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Ranged</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Shark</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="1">
         <v>10006</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
+      <c r="B7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10006_Name</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10006_Desc</t>
+        </is>
       </c>
       <c r="D7" s="1">
         <v>120</v>
@@ -967,7 +936,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="G7" s="1">
         <v>3</v>
@@ -987,22 +956,34 @@
       <c r="L7" s="1">
         <v>2</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="M7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Turtle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="1">
         <v>10007</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
+      <c r="B8" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10007_Name</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10007_Desc</t>
+        </is>
       </c>
       <c r="D8" s="1">
         <v>20</v>
@@ -1031,22 +1012,34 @@
       <c r="L8" s="1">
         <v>3</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="M8" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Snake</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="1">
         <v>10008</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
+      <c r="B9" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10008_Name</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10008_Desc</t>
+        </is>
       </c>
       <c r="D9" s="1">
         <v>50</v>
@@ -1075,22 +1068,34 @@
       <c r="L9" s="1">
         <v>1.5</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="M9" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Panda</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="1">
         <v>10009</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>46</v>
+      <c r="B10" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10009_Name</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10009_Desc</t>
+        </is>
       </c>
       <c r="D10" s="1">
         <v>80</v>
@@ -1099,7 +1104,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="1">
-        <v>4.2999999999999998</v>
+        <v>4.3</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1119,22 +1124,34 @@
       <c r="L10" s="1">
         <v>1.5</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="M10" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Lizard</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="1">
         <v>10010</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
+      <c r="B11" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10010_Name</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10010_Desc</t>
+        </is>
       </c>
       <c r="D11" s="1">
         <v>130</v>
@@ -1163,22 +1180,34 @@
       <c r="L11" s="1">
         <v>2</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="M11" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Bear</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="1">
         <v>10011</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>47</v>
+      <c r="B12" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10011_Name</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10011_Desc</t>
+        </is>
       </c>
       <c r="D12" s="1">
         <v>10</v>
@@ -1190,7 +1219,7 @@
         <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0.80000000000000004</v>
+        <v>0.8</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -1207,22 +1236,34 @@
       <c r="L12" s="1">
         <v>2</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="M12" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Dwarf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="1">
         <v>10012</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>11</v>
+      <c r="B13" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10012_Name</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10012_Desc</t>
+        </is>
       </c>
       <c r="D13" s="1">
         <v>40</v>
@@ -1234,7 +1275,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>1.3999999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="H13" s="1">
         <v>30</v>
@@ -1251,22 +1292,34 @@
       <c r="L13" s="1">
         <v>3</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="M13" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Spider</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="1">
         <v>10013</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>31</v>
+      <c r="B14" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10013_Name</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10013_Desc</t>
+        </is>
       </c>
       <c r="D14" s="1">
         <v>160</v>
@@ -1295,22 +1348,34 @@
       <c r="L14" s="1">
         <v>2</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="M14" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Minotaur</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="1">
         <v>10014</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>13</v>
+      <c r="B15" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10014_Name</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10014_Desc</t>
+        </is>
       </c>
       <c r="D15" s="1">
         <v>28</v>
@@ -1339,22 +1404,34 @@
       <c r="L15" s="1">
         <v>2</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="M15" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">GoblinSpear</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="1">
         <v>10015</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>16</v>
+      <c r="B16" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10015_Name</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10015_Desc</t>
+        </is>
       </c>
       <c r="D16" s="1">
         <v>60</v>
@@ -1383,22 +1460,34 @@
       <c r="L16" s="1">
         <v>5</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="M16" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Ranged</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">GoblinSorcerer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="1">
         <v>10016</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>28</v>
+      <c r="B17" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10016_Name</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10016_Desc</t>
+        </is>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -1427,22 +1516,38 @@
       <c r="L17" s="1">
         <v>2</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="M17" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">GiantGoblin</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22">
       <c r="A22" s="1">
         <v>10100</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>44</v>
+      <c r="B22" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10100_Name</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Monster_10100_Desc</t>
+        </is>
       </c>
       <c r="D22" s="1">
         <v>500</v>
@@ -1454,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="G22" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H22" s="1">
         <v>1000</v>
@@ -1471,11 +1576,17 @@
       <c r="L22" s="1">
         <v>3</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>21</v>
+      <c r="M22" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Melee</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">SkullKing</t>
+        </is>
       </c>
       <c r="O22" s="1"/>
     </row>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -1,18 +1,212 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600"/>
+    <workbookView windowWidth="28545" windowHeight="11700"/>
   </bookViews>
   <sheets>
-    <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10015_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10015_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57,7 +251,7 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -82,11 +276,69 @@
       </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+  <cellStyleXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -171,74 +423,6 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -525,12 +709,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet1">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="15.5" customWidth="1"/>
@@ -547,107 +728,59 @@
     <col min="14" max="14" width="13.35546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <v>monster_name</v>
-        <is>
-          <t xml:space="preserve">monster_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <v>damage</v>
-        <is>
-          <t xml:space="preserve">damage</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <v>move_speed</v>
-        <is>
-          <t xml:space="preserve">move_speed</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <v>attack_delay</v>
-        <is>
-          <t xml:space="preserve">attack_delay</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <v>drop_exp_min</v>
-        <is>
-          <t xml:space="preserve">drop_exp_min</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <v>drop_exp_max</v>
-        <is>
-          <t xml:space="preserve">drop_exp_max</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <v>drop_money_min</v>
-        <is>
-          <t xml:space="preserve">drop_money_min</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <v>drop_money_max</v>
-        <is>
-          <t xml:space="preserve">drop_money_max</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <v>attack_range</v>
-        <is>
-          <t xml:space="preserve">attack_range</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <v>attack_type</v>
-        <is>
-          <t xml:space="preserve">attack_type</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <v>prefab_id</v>
-        <is>
-          <t xml:space="preserve">prefab_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="1">
         <v>10001</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10001_Name</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10001_Desc</t>
-        </is>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -676,34 +809,22 @@
       <c r="L2" s="1">
         <v>2</v>
       </c>
-      <c r="M2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Skull</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="M2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1">
         <v>10002</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10002_Name</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10002_Desc</t>
-        </is>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D3" s="1">
         <v>25</v>
@@ -715,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="1">
-        <v>0.7</v>
+        <v>0.69999999999999996</v>
       </c>
       <c r="H3" s="1">
         <v>30</v>
@@ -732,34 +853,22 @@
       <c r="L3" s="1">
         <v>1.5</v>
       </c>
-      <c r="M3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Thief</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="M3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1">
         <v>10003</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10003_Name</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10003_Desc</t>
-        </is>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D4" s="1">
         <v>40</v>
@@ -771,7 +880,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>2.7</v>
+        <v>2.7000000000000002</v>
       </c>
       <c r="H4" s="1">
         <v>40</v>
@@ -788,34 +897,22 @@
       <c r="L4" s="1">
         <v>6</v>
       </c>
-      <c r="M4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Ranged</t>
-        </is>
-      </c>
-      <c r="N4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Gnoll</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+      <c r="M4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>10004</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10004_Name</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10004_Desc</t>
-        </is>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -844,34 +941,22 @@
       <c r="L5" s="1">
         <v>2</v>
       </c>
-      <c r="M5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Hammershark</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="M5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>10005</v>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10005_Name</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10005_Desc</t>
-        </is>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D6" s="1">
         <v>35</v>
@@ -900,34 +985,22 @@
       <c r="L6" s="1">
         <v>5</v>
       </c>
-      <c r="M6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Ranged</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Shark</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+      <c r="M6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1">
         <v>10006</v>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10006_Name</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10006_Desc</t>
-        </is>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
@@ -936,7 +1009,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G7" s="1">
         <v>3</v>
@@ -956,34 +1029,22 @@
       <c r="L7" s="1">
         <v>2</v>
       </c>
-      <c r="M7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Turtle</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="M7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1">
         <v>10007</v>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10007_Name</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10007_Desc</t>
-        </is>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="1">
         <v>20</v>
@@ -1010,36 +1071,24 @@
         <v>18</v>
       </c>
       <c r="L8" s="1">
-        <v>3</v>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Snake</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+        <v>2</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="1">
         <v>10008</v>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10008_Name</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10008_Desc</t>
-        </is>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D9" s="1">
         <v>50</v>
@@ -1068,34 +1117,22 @@
       <c r="L9" s="1">
         <v>1.5</v>
       </c>
-      <c r="M9" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N9" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Panda</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+      <c r="M9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="1">
         <v>10009</v>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10009_Name</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10009_Desc</t>
-        </is>
+      <c r="B10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D10" s="1">
         <v>80</v>
@@ -1104,7 +1141,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="1">
-        <v>4.3</v>
+        <v>4.2999999999999998</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1124,34 +1161,22 @@
       <c r="L10" s="1">
         <v>1.5</v>
       </c>
-      <c r="M10" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N10" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Lizard</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+      <c r="M10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="1">
         <v>10010</v>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10010_Name</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10010_Desc</t>
-        </is>
+      <c r="B11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D11" s="1">
         <v>130</v>
@@ -1180,34 +1205,22 @@
       <c r="L11" s="1">
         <v>2</v>
       </c>
-      <c r="M11" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Bear</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="M11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="1">
         <v>10011</v>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10011_Name</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10011_Desc</t>
-        </is>
+      <c r="B12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D12" s="1">
         <v>10</v>
@@ -1219,7 +1232,7 @@
         <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0.8</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="H12" s="1">
         <v>11</v>
@@ -1236,34 +1249,22 @@
       <c r="L12" s="1">
         <v>2</v>
       </c>
-      <c r="M12" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Dwarf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+      <c r="M12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="1">
         <v>10012</v>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10012_Name</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10012_Desc</t>
-        </is>
+      <c r="B13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D13" s="1">
         <v>40</v>
@@ -1275,7 +1276,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>1.4</v>
+        <v>1.3999999999999999</v>
       </c>
       <c r="H13" s="1">
         <v>30</v>
@@ -1292,34 +1293,22 @@
       <c r="L13" s="1">
         <v>3</v>
       </c>
-      <c r="M13" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Spider</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+      <c r="M13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="1">
         <v>10013</v>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10013_Name</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10013_Desc</t>
-        </is>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D14" s="1">
         <v>160</v>
@@ -1348,34 +1337,22 @@
       <c r="L14" s="1">
         <v>2</v>
       </c>
-      <c r="M14" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N14" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Minotaur</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+      <c r="M14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="1">
         <v>10014</v>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10014_Name</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10014_Desc</t>
-        </is>
+      <c r="B15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D15" s="1">
         <v>28</v>
@@ -1404,34 +1381,22 @@
       <c r="L15" s="1">
         <v>2</v>
       </c>
-      <c r="M15" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N15" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">GoblinSpear</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+      <c r="M15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="1">
         <v>10015</v>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10015_Name</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10015_Desc</t>
-        </is>
+      <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D16" s="1">
         <v>60</v>
@@ -1460,34 +1425,22 @@
       <c r="L16" s="1">
         <v>5</v>
       </c>
-      <c r="M16" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Ranged</t>
-        </is>
-      </c>
-      <c r="N16" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">GoblinSorcerer</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+      <c r="M16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="1">
         <v>10016</v>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10016_Name</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10016_Desc</t>
-        </is>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -1516,78 +1469,28 @@
       <c r="L17" s="1">
         <v>2</v>
       </c>
-      <c r="M17" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N17" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">GiantGoblin</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="1">
-        <v>10100</v>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10100_Name</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Monster_10100_Desc</t>
-        </is>
-      </c>
-      <c r="D22" s="1">
-        <v>500</v>
-      </c>
-      <c r="E22" s="1">
-        <v>100</v>
-      </c>
-      <c r="F22" s="1">
-        <v>8</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1000</v>
-      </c>
-      <c r="J22" s="1">
-        <v>10000</v>
-      </c>
-      <c r="K22" s="1">
-        <v>10000</v>
-      </c>
-      <c r="L22" s="1">
-        <v>3</v>
-      </c>
-      <c r="M22" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Melee</t>
-        </is>
-      </c>
-      <c r="N22" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">SkullKing</t>
-        </is>
-      </c>
+      <c r="M17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
   <si>
     <t xml:space="preserve">attack_delay</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="64">
   <si>
     <t xml:space="preserve">attack_delay</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -13,35 +13,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
     <t xml:space="preserve">attack_delay</t>
   </si>
   <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
     <t xml:space="preserve">drop_exp_min</t>
   </si>
   <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
     <t xml:space="preserve">drop_exp_max</t>
   </si>
   <si>
     <t xml:space="preserve">GoblinSorcerer</t>
   </si>
   <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Desc</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monster_10002_Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Monster_10007_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monster_10003_Name</t>
   </si>
   <si>
@@ -51,160 +72,139 @@
     <t xml:space="preserve">Monster_10004_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10002_Desc</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monster_10001_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Name</t>
+    <t xml:space="preserve">Monster_10015_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Desc</t>
   </si>
   <si>
     <t xml:space="preserve">Monster_10006_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10007_Desc</t>
+    <t xml:space="preserve">Monster_10015_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Monster_10004_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Desc</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monster_10014_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10013_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monster_10009_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10010_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10010_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
   </si>
   <si>
     <t xml:space="preserve">GiantGoblin</t>
   </si>
   <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
     <t xml:space="preserve">Minotaur</t>
   </si>
   <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
   </si>
   <si>
     <t xml:space="preserve">max_hp</t>
   </si>
   <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
     <t xml:space="preserve">damage</t>
   </si>
   <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
   </si>
   <si>
     <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
   </si>
 </sst>
 </file>
@@ -730,19 +730,19 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>44</v>
@@ -751,25 +751,25 @@
         <v>0</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -777,10 +777,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -810,10 +810,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -821,10 +821,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1">
         <v>25</v>
@@ -854,10 +854,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -865,10 +865,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1">
         <v>40</v>
@@ -898,10 +898,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -909,10 +909,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -942,10 +942,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -953,10 +953,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1">
         <v>35</v>
@@ -965,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="1">
-        <v>3</v>
+        <v>3.3999999999999999</v>
       </c>
       <c r="G6" s="1">
         <v>3</v>
@@ -986,10 +986,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -997,10 +997,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
@@ -1009,7 +1009,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="G7" s="1">
         <v>3</v>
@@ -1030,10 +1030,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1044,7 +1044,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1">
         <v>20</v>
@@ -1074,10 +1074,10 @@
         <v>2</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1085,10 +1085,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1">
         <v>50</v>
@@ -1118,10 +1118,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1129,10 +1129,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1">
         <v>80</v>
@@ -1162,10 +1162,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1173,10 +1173,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="D11" s="1">
         <v>130</v>
@@ -1206,10 +1206,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1217,7 +1217,7 @@
         <v>10011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>36</v>
@@ -1250,7 +1250,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>62</v>
@@ -1261,10 +1261,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1">
         <v>40</v>
@@ -1294,10 +1294,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1305,10 +1305,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1">
         <v>160</v>
@@ -1338,10 +1338,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1349,10 +1349,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D15" s="1">
         <v>28</v>
@@ -1382,10 +1382,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1393,10 +1393,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1">
         <v>60</v>
@@ -1426,7 +1426,7 @@
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>7</v>
@@ -1437,10 +1437,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -1449,7 +1449,7 @@
         <v>20</v>
       </c>
       <c r="F17" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -1470,10 +1470,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:15">

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -15,196 +15,196 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10015_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10015_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
     <t xml:space="preserve">attack_delay</t>
   </si>
   <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
     <t xml:space="preserve">drop_money_max</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
     <t xml:space="preserve">drop_exp_max</t>
   </si>
   <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10010_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10010_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
   </si>
   <si>
     <t xml:space="preserve">Melee</t>
   </si>
   <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
   </si>
   <si>
     <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
   </si>
 </sst>
 </file>
@@ -730,46 +730,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -777,10 +777,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -810,10 +810,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -821,10 +821,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1">
         <v>25</v>
@@ -854,10 +854,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -865,10 +865,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1">
         <v>40</v>
@@ -898,10 +898,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -909,10 +909,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -942,10 +942,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -953,10 +953,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1">
         <v>35</v>
@@ -986,10 +986,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -997,13 +997,13 @@
         <v>10006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E7" s="1">
         <v>15</v>
@@ -1030,10 +1030,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1041,10 +1041,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1">
         <v>20</v>
@@ -1074,7 +1074,7 @@
         <v>2</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>50</v>
@@ -1085,10 +1085,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1">
         <v>50</v>
@@ -1118,10 +1118,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1129,10 +1129,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1">
         <v>80</v>
@@ -1162,10 +1162,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1173,10 +1173,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1">
         <v>130</v>
@@ -1206,10 +1206,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1217,10 +1217,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1">
         <v>10</v>
@@ -1229,7 +1229,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="1">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G12" s="1">
         <v>0.80000000000000004</v>
@@ -1250,10 +1250,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1261,10 +1261,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1">
         <v>40</v>
@@ -1294,10 +1294,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1305,10 +1305,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1">
         <v>160</v>
@@ -1338,10 +1338,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1349,10 +1349,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1">
         <v>28</v>
@@ -1382,10 +1382,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1393,10 +1393,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D16" s="1">
         <v>60</v>
@@ -1426,10 +1426,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1437,10 +1437,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -1470,10 +1470,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:15">

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -15,70 +15,109 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
+    <t xml:space="preserve">Monster_10016_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10015_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monster_10007_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Desc</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monster_10002_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Desc</t>
+    <t xml:space="preserve">Monster_10001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Monster_10015_Desc</t>
@@ -87,124 +126,85 @@
     <t xml:space="preserve">Monster_10011_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10005_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monster_10010_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10010_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Desc</t>
+    <t xml:space="preserve">Monster_10011_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Monster_10004_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10012_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Desc</t>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
   </si>
   <si>
     <t xml:space="preserve">attack_type</t>
   </si>
   <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
     <t xml:space="preserve">GoblinSpear</t>
   </si>
   <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
     <t xml:space="preserve">prefab_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
     <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
   </si>
 </sst>
 </file>
@@ -730,46 +730,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -777,10 +777,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -810,10 +810,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -821,10 +821,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1">
         <v>25</v>
@@ -854,10 +854,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -865,10 +865,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1">
         <v>40</v>
@@ -898,10 +898,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -909,10 +909,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -942,10 +942,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -953,10 +953,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1">
         <v>35</v>
@@ -986,10 +986,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -997,10 +997,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1">
         <v>170</v>
@@ -1030,10 +1030,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1041,10 +1041,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1">
         <v>20</v>
@@ -1074,10 +1074,10 @@
         <v>2</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1085,10 +1085,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1">
         <v>50</v>
@@ -1118,10 +1118,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1129,10 +1129,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>80</v>
@@ -1162,10 +1162,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1173,10 +1173,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1">
         <v>130</v>
@@ -1206,10 +1206,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1217,10 +1217,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1">
         <v>10</v>
@@ -1250,10 +1250,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1261,10 +1261,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1">
         <v>40</v>
@@ -1294,10 +1294,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1305,10 +1305,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="D14" s="1">
         <v>160</v>
@@ -1317,7 +1317,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="1">
-        <v>5</v>
+        <v>4.7000000000000002</v>
       </c>
       <c r="G14" s="1">
         <v>2</v>
@@ -1338,10 +1338,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1349,10 +1349,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1">
         <v>28</v>
@@ -1382,10 +1382,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1393,10 +1393,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>60</v>
@@ -1426,10 +1426,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1437,10 +1437,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -1470,10 +1470,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:15">

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
   <si>
     <t xml:space="preserve">attack_range</t>
   </si>
@@ -827,7 +827,7 @@
         <v>29</v>
       </c>
       <c r="D3" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1">
         <v>5</v>
@@ -871,7 +871,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E4" s="1">
         <v>15</v>
@@ -883,16 +883,16 @@
         <v>2.7000000000000002</v>
       </c>
       <c r="H4" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I4" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J4" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K4" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L4" s="1">
         <v>6</v>
@@ -927,10 +927,10 @@
         <v>2</v>
       </c>
       <c r="H5" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I5" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J5" s="1">
         <v>20</v>
@@ -971,16 +971,16 @@
         <v>3</v>
       </c>
       <c r="H6" s="1">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="I6" s="1">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J6" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K6" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="L6" s="1">
         <v>5</v>
@@ -1015,16 +1015,16 @@
         <v>3</v>
       </c>
       <c r="H7" s="1">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="I7" s="1">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="J7" s="1">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="K7" s="1">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="L7" s="1">
         <v>2</v>
@@ -1047,7 +1047,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -1091,7 +1091,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
@@ -1135,7 +1135,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="1">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
@@ -1147,16 +1147,16 @@
         <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I10" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J10" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K10" s="1">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L10" s="1">
         <v>1.5</v>
@@ -1179,7 +1179,7 @@
         <v>37</v>
       </c>
       <c r="D11" s="1">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="E11" s="1">
         <v>30</v>
@@ -1191,16 +1191,16 @@
         <v>2.5</v>
       </c>
       <c r="H11" s="1">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="I11" s="1">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="J11" s="1">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="K11" s="1">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L11" s="1">
         <v>2</v>
@@ -1223,7 +1223,7 @@
         <v>38</v>
       </c>
       <c r="D12" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -1235,16 +1235,16 @@
         <v>0.80000000000000004</v>
       </c>
       <c r="H12" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I12" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J12" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K12" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L12" s="1">
         <v>2</v>
@@ -1267,7 +1267,7 @@
         <v>14</v>
       </c>
       <c r="D13" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1">
         <v>15</v>
@@ -1279,16 +1279,16 @@
         <v>1.3999999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J13" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K13" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L13" s="1">
         <v>3</v>
@@ -1311,7 +1311,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="1">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="E14" s="1">
         <v>20</v>
@@ -1323,16 +1323,16 @@
         <v>2</v>
       </c>
       <c r="H14" s="1">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="I14" s="1">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="J14" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="K14" s="1">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="L14" s="1">
         <v>2</v>
@@ -1367,16 +1367,16 @@
         <v>2</v>
       </c>
       <c r="H15" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I15" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J15" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K15" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L15" s="1">
         <v>2</v>
@@ -1411,16 +1411,16 @@
         <v>3</v>
       </c>
       <c r="H16" s="1">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="I16" s="1">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="J16" s="1">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="K16" s="1">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
@@ -1455,16 +1455,16 @@
         <v>4</v>
       </c>
       <c r="H17" s="1">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="I17" s="1">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="J17" s="1">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="K17" s="1">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="L17" s="1">
         <v>2</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -13,198 +13,198 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
   <si>
     <t xml:space="preserve">attack_range</t>
   </si>
   <si>
-    <t xml:space="preserve">drop_exp_min</t>
+    <t xml:space="preserve">drop_money_max</t>
   </si>
   <si>
     <t xml:space="preserve">monster_name</t>
   </si>
   <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
     <t xml:space="preserve">drop_exp_max</t>
   </si>
   <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
     <t xml:space="preserve">GoblinSorcerer</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10015_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Desc</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monster_10016_Desc</t>
   </si>
   <si>
+    <t xml:space="preserve">Monster_10009_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Desc</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monster_10015_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10009_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10010_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10010_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10004_Name</t>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
   </si>
   <si>
     <t xml:space="preserve">Snake</t>
   </si>
   <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
     <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
   </si>
 </sst>
 </file>
@@ -717,6 +717,7 @@
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="9.00390625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" customWidth="1"/>
     <col min="7" max="7" width="11.2109375" customWidth="1"/>
     <col min="8" max="8" width="12.85546875" customWidth="1"/>
@@ -733,43 +734,43 @@
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -777,10 +778,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -810,10 +811,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -821,7 +822,7 @@
         <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -854,10 +855,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -865,10 +866,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1">
         <v>45</v>
@@ -898,10 +899,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -909,10 +910,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -942,10 +943,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -953,10 +954,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1">
         <v>35</v>
@@ -986,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -997,10 +998,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1">
         <v>170</v>
@@ -1030,10 +1031,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1041,10 +1042,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1">
         <v>18</v>
@@ -1074,10 +1075,10 @@
         <v>2</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1085,10 +1086,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1">
         <v>45</v>
@@ -1118,10 +1119,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1129,10 +1130,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D10" s="1">
         <v>70</v>
@@ -1162,10 +1163,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1173,10 +1174,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1">
         <v>110</v>
@@ -1206,10 +1207,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1217,16 +1218,16 @@
         <v>10011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1">
         <v>8</v>
       </c>
       <c r="E12" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12" s="1">
         <v>6.5</v>
@@ -1250,10 +1251,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1261,10 +1262,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1">
         <v>35</v>
@@ -1294,10 +1295,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1305,10 +1306,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1">
         <v>110</v>
@@ -1338,10 +1339,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1349,10 +1350,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1">
         <v>28</v>
@@ -1382,10 +1383,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1393,7 +1394,7 @@
         <v>10015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>35</v>
@@ -1426,10 +1427,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1437,10 +1438,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -1470,10 +1471,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:15">

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -15,196 +15,196 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10014_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10015_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10015_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10013_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10016_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10009_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10012_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10008_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10010_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10011_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster_10005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
     <t xml:space="preserve">attack_delay</t>
   </si>
   <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10010_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10010_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Name</t>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
   </si>
   <si>
     <t xml:space="preserve">Thief</t>
   </si>
   <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ranged</t>
   </si>
   <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
     <t xml:space="preserve">Panda</t>
   </si>
   <si>
-    <t xml:space="preserve">Spider</t>
+    <t xml:space="preserve">Bear</t>
   </si>
   <si>
     <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
   </si>
 </sst>
 </file>
@@ -731,46 +731,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -778,16 +778,16 @@
         <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
       </c>
       <c r="E2" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -811,10 +811,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -822,10 +822,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1">
         <v>30</v>
@@ -855,10 +855,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -866,10 +866,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1">
         <v>45</v>
@@ -899,10 +899,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -910,10 +910,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -943,10 +943,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -954,10 +954,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1">
         <v>35</v>
@@ -987,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -998,10 +998,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1">
         <v>170</v>
@@ -1031,10 +1031,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1042,10 +1042,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1">
         <v>18</v>
@@ -1075,10 +1075,10 @@
         <v>2</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1086,10 +1086,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1">
         <v>45</v>
@@ -1119,10 +1119,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1130,10 +1130,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D10" s="1">
         <v>70</v>
@@ -1163,10 +1163,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1174,10 +1174,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1">
         <v>110</v>
@@ -1207,10 +1207,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1218,10 +1218,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D12" s="1">
         <v>8</v>
@@ -1251,10 +1251,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1262,10 +1262,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D13" s="1">
         <v>35</v>
@@ -1295,10 +1295,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1306,10 +1306,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D14" s="1">
         <v>110</v>
@@ -1339,10 +1339,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1350,10 +1350,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1">
         <v>28</v>
@@ -1383,10 +1383,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1394,10 +1394,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1">
         <v>60</v>
@@ -1427,10 +1427,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1438,10 +1438,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -1471,10 +1471,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:15">

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="64">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -828,7 +828,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1">
         <v>5</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1">
         <v>15</v>
@@ -896,7 +896,7 @@
         <v>45</v>
       </c>
       <c r="L4" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>60</v>
@@ -960,7 +960,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
@@ -1004,7 +1004,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="1">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E7" s="1">
         <v>15</v>
@@ -1048,7 +1048,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -1136,7 +1136,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
@@ -1268,7 +1268,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1">
         <v>15</v>
@@ -1400,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E16" s="1">
         <v>15</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -960,7 +960,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
@@ -1136,7 +1136,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
@@ -1268,10 +1268,10 @@
         <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F13" s="1">
         <v>5</v>
@@ -1356,7 +1356,7 @@
         <v>7</v>
       </c>
       <c r="D15" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -784,10 +784,10 @@
         <v>23</v>
       </c>
       <c r="D2" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -802,10 +802,10 @@
         <v>10</v>
       </c>
       <c r="J2" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L2" s="1">
         <v>2</v>
@@ -828,13 +828,13 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
         <v>0.69999999999999996</v>
@@ -846,10 +846,10 @@
         <v>30</v>
       </c>
       <c r="J3" s="1">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K3" s="1">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1">
         <v>1.5</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1">
         <v>15</v>
@@ -881,19 +881,19 @@
         <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>2.7000000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="H4" s="1">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I4" s="1">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="J4" s="1">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="K4" s="1">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="L4" s="1">
         <v>5</v>
@@ -916,7 +916,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1">
         <v>10</v>
@@ -934,10 +934,10 @@
         <v>20</v>
       </c>
       <c r="J5" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L5" s="1">
         <v>2</v>
@@ -960,28 +960,28 @@
         <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1">
         <v>3.3999999999999999</v>
       </c>
       <c r="G6" s="1">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="H6" s="1">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="I6" s="1">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J6" s="1">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K6" s="1">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="L6" s="1">
         <v>5</v>
@@ -1004,16 +1004,16 @@
         <v>26</v>
       </c>
       <c r="D7" s="1">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="E7" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1">
         <v>2.7999999999999998</v>
       </c>
       <c r="G7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="1">
         <v>170</v>
@@ -1022,10 +1022,10 @@
         <v>170</v>
       </c>
       <c r="J7" s="1">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="K7" s="1">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="L7" s="1">
         <v>2</v>
@@ -1048,10 +1048,10 @@
         <v>17</v>
       </c>
       <c r="D8" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1">
         <v>5</v>
@@ -1066,10 +1066,10 @@
         <v>18</v>
       </c>
       <c r="J8" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K8" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L8" s="1">
         <v>2</v>
@@ -1092,7 +1092,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
@@ -1110,10 +1110,10 @@
         <v>45</v>
       </c>
       <c r="J9" s="1">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="K9" s="1">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="L9" s="1">
         <v>1.5</v>
@@ -1136,13 +1136,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
       </c>
       <c r="F10" s="1">
-        <v>4.2999999999999998</v>
+        <v>3.7</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1154,10 +1154,10 @@
         <v>70</v>
       </c>
       <c r="J10" s="1">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="K10" s="1">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="L10" s="1">
         <v>1.5</v>
@@ -1198,10 +1198,10 @@
         <v>110</v>
       </c>
       <c r="J11" s="1">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="K11" s="1">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="L11" s="1">
         <v>2</v>
@@ -1224,7 +1224,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -1236,16 +1236,16 @@
         <v>0.80000000000000004</v>
       </c>
       <c r="H12" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I12" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J12" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K12" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L12" s="1">
         <v>2</v>
@@ -1268,28 +1268,28 @@
         <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>1.3999999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="H13" s="1">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I13" s="1">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J13" s="1">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K13" s="1">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="L13" s="1">
         <v>3</v>
@@ -1312,28 +1312,28 @@
         <v>15</v>
       </c>
       <c r="D14" s="1">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="E14" s="1">
         <v>20</v>
       </c>
       <c r="F14" s="1">
-        <v>4.7000000000000002</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
         <v>2</v>
       </c>
       <c r="H14" s="1">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I14" s="1">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J14" s="1">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="K14" s="1">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="L14" s="1">
         <v>2</v>
@@ -1356,7 +1356,7 @@
         <v>7</v>
       </c>
       <c r="D15" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
@@ -1374,10 +1374,10 @@
         <v>28</v>
       </c>
       <c r="J15" s="1">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K15" s="1">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="L15" s="1">
         <v>2</v>
@@ -1400,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E16" s="1">
         <v>15</v>
@@ -1412,16 +1412,16 @@
         <v>3</v>
       </c>
       <c r="H16" s="1">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I16" s="1">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J16" s="1">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="K16" s="1">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
@@ -1444,16 +1444,16 @@
         <v>10</v>
       </c>
       <c r="D17" s="1">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="E17" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
       </c>
       <c r="G17" s="1">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="H17" s="1">
         <v>220</v>
@@ -1462,10 +1462,10 @@
         <v>220</v>
       </c>
       <c r="J17" s="1">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="K17" s="1">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="L17" s="1">
         <v>2</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -784,10 +784,10 @@
         <v>23</v>
       </c>
       <c r="D2" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -796,16 +796,16 @@
         <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2" s="1">
         <v>2</v>
@@ -828,10 +828,10 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="1">
         <v>7</v>
@@ -840,16 +840,16 @@
         <v>0.69999999999999996</v>
       </c>
       <c r="H3" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J3" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K3" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L3" s="1">
         <v>1.5</v>
@@ -872,10 +872,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1">
         <v>4</v>
@@ -884,16 +884,16 @@
         <v>2.4</v>
       </c>
       <c r="H4" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I4" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J4" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K4" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L4" s="1">
         <v>5</v>
@@ -916,10 +916,10 @@
         <v>6</v>
       </c>
       <c r="D5" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1">
         <v>4</v>
@@ -928,16 +928,16 @@
         <v>2</v>
       </c>
       <c r="H5" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I5" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J5" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K5" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L5" s="1">
         <v>2</v>
@@ -960,10 +960,10 @@
         <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1">
         <v>3.3999999999999999</v>
@@ -972,16 +972,16 @@
         <v>2.3</v>
       </c>
       <c r="H6" s="1">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I6" s="1">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J6" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K6" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1">
         <v>5</v>
@@ -1004,10 +1004,10 @@
         <v>26</v>
       </c>
       <c r="D7" s="1">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E7" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1">
         <v>2.7999999999999998</v>
@@ -1016,16 +1016,16 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="I7" s="1">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="J7" s="1">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="K7" s="1">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="L7" s="1">
         <v>2</v>
@@ -1048,10 +1048,10 @@
         <v>17</v>
       </c>
       <c r="D8" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1">
         <v>5</v>
@@ -1060,16 +1060,16 @@
         <v>2</v>
       </c>
       <c r="H8" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L8" s="1">
         <v>2</v>
@@ -1092,10 +1092,10 @@
         <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1">
         <v>6</v>
@@ -1104,16 +1104,16 @@
         <v>1.5</v>
       </c>
       <c r="H9" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I9" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J9" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K9" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L9" s="1">
         <v>1.5</v>
@@ -1136,10 +1136,10 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1">
         <v>3.7</v>
@@ -1148,16 +1148,16 @@
         <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I10" s="1">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J10" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K10" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L10" s="1">
         <v>1.5</v>
@@ -1180,10 +1180,10 @@
         <v>29</v>
       </c>
       <c r="D11" s="1">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="E11" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1">
         <v>7</v>
@@ -1192,16 +1192,16 @@
         <v>2.5</v>
       </c>
       <c r="H11" s="1">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I11" s="1">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="J11" s="1">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K11" s="1">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="L11" s="1">
         <v>2</v>
@@ -1224,10 +1224,10 @@
         <v>31</v>
       </c>
       <c r="D12" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1">
         <v>6.5</v>
@@ -1236,16 +1236,16 @@
         <v>0.80000000000000004</v>
       </c>
       <c r="H12" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I12" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L12" s="1">
         <v>2</v>
@@ -1268,10 +1268,10 @@
         <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F13" s="1">
         <v>4</v>
@@ -1280,16 +1280,16 @@
         <v>1.6</v>
       </c>
       <c r="H13" s="1">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I13" s="1">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J13" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K13" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L13" s="1">
         <v>3</v>
@@ -1312,10 +1312,10 @@
         <v>15</v>
       </c>
       <c r="D14" s="1">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="E14" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F14" s="1">
         <v>4</v>
@@ -1324,16 +1324,16 @@
         <v>2</v>
       </c>
       <c r="H14" s="1">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I14" s="1">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="J14" s="1">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K14" s="1">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L14" s="1">
         <v>2</v>
@@ -1356,10 +1356,10 @@
         <v>7</v>
       </c>
       <c r="D15" s="1">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
@@ -1368,16 +1368,16 @@
         <v>2</v>
       </c>
       <c r="H15" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I15" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J15" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K15" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L15" s="1">
         <v>2</v>
@@ -1400,10 +1400,10 @@
         <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
@@ -1412,16 +1412,16 @@
         <v>3</v>
       </c>
       <c r="H16" s="1">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I16" s="1">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J16" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K16" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
@@ -1444,10 +1444,10 @@
         <v>10</v>
       </c>
       <c r="D17" s="1">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="E17" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -1456,16 +1456,16 @@
         <v>2.3</v>
       </c>
       <c r="H17" s="1">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="I17" s="1">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="J17" s="1">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="K17" s="1">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="L17" s="1">
         <v>2</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -784,10 +784,10 @@
         <v>23</v>
       </c>
       <c r="D2" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -828,16 +828,16 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="G3" s="1">
-        <v>0.69999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="H3" s="1">
         <v>27</v>
@@ -852,7 +852,7 @@
         <v>5</v>
       </c>
       <c r="L3" s="1">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>63</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1">
         <v>12</v>
@@ -881,7 +881,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="H4" s="1">
         <v>32</v>
@@ -916,7 +916,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="1">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1">
         <v>8</v>
@@ -960,16 +960,16 @@
         <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1">
-        <v>3.3999999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="G6" s="1">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="H6" s="1">
         <v>41</v>
@@ -984,7 +984,7 @@
         <v>8</v>
       </c>
       <c r="L6" s="1">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>60</v>
@@ -1004,13 +1004,13 @@
         <v>26</v>
       </c>
       <c r="D7" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E7" s="1">
         <v>16</v>
       </c>
       <c r="F7" s="1">
-        <v>2.7999999999999998</v>
+        <v>3.6</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -1028,7 +1028,7 @@
         <v>31</v>
       </c>
       <c r="L7" s="1">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>63</v>
@@ -1048,16 +1048,16 @@
         <v>17</v>
       </c>
       <c r="D8" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1">
         <v>8</v>
       </c>
       <c r="F8" s="1">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="G8" s="1">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H8" s="1">
         <v>16</v>
@@ -1072,7 +1072,7 @@
         <v>5</v>
       </c>
       <c r="L8" s="1">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>63</v>
@@ -1092,16 +1092,16 @@
         <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" s="1">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="G9" s="1">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H9" s="1">
         <v>40</v>
@@ -1116,7 +1116,7 @@
         <v>8</v>
       </c>
       <c r="L9" s="1">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>63</v>
@@ -1136,13 +1136,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E10" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1160,7 +1160,7 @@
         <v>13</v>
       </c>
       <c r="L10" s="1">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>63</v>
@@ -1180,16 +1180,16 @@
         <v>29</v>
       </c>
       <c r="D11" s="1">
-        <v>88</v>
+        <v>240</v>
       </c>
       <c r="E11" s="1">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F11" s="1">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="G11" s="1">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H11" s="1">
         <v>99</v>
@@ -1224,16 +1224,16 @@
         <v>31</v>
       </c>
       <c r="D12" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="G12" s="1">
-        <v>0.80000000000000004</v>
+        <v>0.7</v>
       </c>
       <c r="H12" s="1">
         <v>9</v>
@@ -1248,7 +1248,7 @@
         <v>4</v>
       </c>
       <c r="L12" s="1">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>63</v>
@@ -1268,13 +1268,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1">
         <v>10</v>
       </c>
       <c r="F13" s="1">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="G13" s="1">
         <v>1.6</v>
@@ -1292,7 +1292,7 @@
         <v>7</v>
       </c>
       <c r="L13" s="1">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>63</v>
@@ -1312,13 +1312,13 @@
         <v>15</v>
       </c>
       <c r="D14" s="1">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="E14" s="1">
         <v>16</v>
       </c>
       <c r="F14" s="1">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G14" s="1">
         <v>2</v>
@@ -1356,13 +1356,13 @@
         <v>7</v>
       </c>
       <c r="D15" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1">
         <v>8</v>
       </c>
       <c r="F15" s="1">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -1400,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E16" s="1">
         <v>12</v>
@@ -1409,7 +1409,7 @@
         <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="H16" s="1">
         <v>62</v>
@@ -1444,13 +1444,13 @@
         <v>10</v>
       </c>
       <c r="D17" s="1">
-        <v>206</v>
+        <v>132</v>
       </c>
       <c r="E17" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F17" s="1">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G17" s="1">
         <v>2.3</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -796,10 +796,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="1">
         <v>2</v>
@@ -828,7 +828,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1">
         <v>4</v>
@@ -840,10 +840,10 @@
         <v>0.6</v>
       </c>
       <c r="H3" s="1">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J3" s="1">
         <v>5</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1">
         <v>12</v>
@@ -884,16 +884,16 @@
         <v>2</v>
       </c>
       <c r="H4" s="1">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I4" s="1">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J4" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K4" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L4" s="1">
         <v>5</v>
@@ -928,16 +928,16 @@
         <v>2</v>
       </c>
       <c r="H5" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I5" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J5" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5" s="1">
         <v>2</v>
@@ -960,7 +960,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
@@ -972,16 +972,16 @@
         <v>1.9</v>
       </c>
       <c r="H6" s="1">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I6" s="1">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J6" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K6" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L6" s="1">
         <v>4.8</v>
@@ -1004,7 +1004,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="1">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E7" s="1">
         <v>16</v>
@@ -1016,16 +1016,16 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="I7" s="1">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="J7" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K7" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L7" s="1">
         <v>2.2</v>
@@ -1066,10 +1066,10 @@
         <v>16</v>
       </c>
       <c r="J8" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="1">
         <v>2.3</v>
@@ -1092,7 +1092,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
@@ -1110,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="J9" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L9" s="1">
         <v>1.7</v>
@@ -1136,7 +1136,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
@@ -1148,16 +1148,16 @@
         <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="I10" s="1">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="J10" s="1">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K10" s="1">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L10" s="1">
         <v>1.7</v>
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="D11" s="1">
-        <v>240</v>
+        <v>168</v>
       </c>
       <c r="E11" s="1">
         <v>40</v>
@@ -1192,16 +1192,16 @@
         <v>2</v>
       </c>
       <c r="H11" s="1">
-        <v>99</v>
+        <v>336</v>
       </c>
       <c r="I11" s="1">
-        <v>99</v>
+        <v>336</v>
       </c>
       <c r="J11" s="1">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="K11" s="1">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="L11" s="1">
         <v>2</v>
@@ -1236,16 +1236,16 @@
         <v>0.7</v>
       </c>
       <c r="H12" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I12" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L12" s="1">
         <v>1.6</v>
@@ -1268,7 +1268,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1">
         <v>10</v>
@@ -1280,16 +1280,16 @@
         <v>1.6</v>
       </c>
       <c r="H13" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I13" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J13" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K13" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L13" s="1">
         <v>2.6</v>
@@ -1312,7 +1312,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1">
         <v>16</v>
@@ -1324,16 +1324,16 @@
         <v>2</v>
       </c>
       <c r="H14" s="1">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="I14" s="1">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="J14" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="1">
         <v>2</v>
@@ -1368,16 +1368,16 @@
         <v>2</v>
       </c>
       <c r="H15" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I15" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K15" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L15" s="1">
         <v>2</v>
@@ -1400,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1">
         <v>12</v>
@@ -1412,16 +1412,16 @@
         <v>2.7</v>
       </c>
       <c r="H16" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I16" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J16" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K16" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
@@ -1444,7 +1444,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="1">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="E17" s="1">
         <v>20</v>
@@ -1456,16 +1456,16 @@
         <v>2.3</v>
       </c>
       <c r="H17" s="1">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="I17" s="1">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="J17" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K17" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L17" s="1">
         <v>2</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -828,7 +828,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1">
         <v>4</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1">
         <v>12</v>
@@ -960,7 +960,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
@@ -1004,7 +1004,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="1">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="E7" s="1">
         <v>16</v>
@@ -1092,7 +1092,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
@@ -1136,7 +1136,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
@@ -1268,7 +1268,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1">
         <v>10</v>
@@ -1312,7 +1312,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E14" s="1">
         <v>16</v>
@@ -1400,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E16" s="1">
         <v>12</v>
@@ -1444,7 +1444,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="1">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="E17" s="1">
         <v>20</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -790,7 +790,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="1">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="1">
-        <v>6.3</v>
+        <v>5.0</v>
       </c>
       <c r="G3" s="1">
         <v>0.6</v>
@@ -878,7 +878,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
@@ -896,7 +896,7 @@
         <v>13</v>
       </c>
       <c r="L4" s="1">
-        <v>5</v>
+        <v>4.0</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>60</v>
@@ -922,7 +922,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="1">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="G5" s="1">
         <v>2</v>
@@ -966,7 +966,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="1">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="G6" s="1">
         <v>1.9</v>
@@ -984,7 +984,7 @@
         <v>13</v>
       </c>
       <c r="L6" s="1">
-        <v>4.8</v>
+        <v>4.0</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>60</v>
@@ -1054,7 +1054,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="1">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="G8" s="1">
         <v>2.1</v>
@@ -1098,7 +1098,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="1">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="G9" s="1">
         <v>1.4</v>
@@ -1142,7 +1142,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="1">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1230,7 +1230,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="G12" s="1">
         <v>0.7</v>
@@ -1274,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="F13" s="1">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="G13" s="1">
         <v>1.6</v>
@@ -1318,7 +1318,7 @@
         <v>16</v>
       </c>
       <c r="F14" s="1">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="G14" s="1">
         <v>2</v>
@@ -1362,7 +1362,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="1">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -1406,7 +1406,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="1">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="G16" s="1">
         <v>2.7</v>
@@ -1424,7 +1424,7 @@
         <v>15</v>
       </c>
       <c r="L16" s="1">
-        <v>5</v>
+        <v>4.0</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>60</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -784,7 +784,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1">
         <v>4</v>
@@ -828,7 +828,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1">
         <v>4</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1">
         <v>12</v>
@@ -916,7 +916,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="1">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1">
         <v>8</v>
@@ -960,7 +960,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
@@ -1004,7 +1004,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="1">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="E7" s="1">
         <v>16</v>
@@ -1048,7 +1048,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="1">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1">
         <v>8</v>
@@ -1092,7 +1092,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
@@ -1136,7 +1136,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="D11" s="1">
-        <v>168</v>
+        <v>252</v>
       </c>
       <c r="E11" s="1">
         <v>40</v>
@@ -1224,7 +1224,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -1268,7 +1268,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E13" s="1">
         <v>10</v>
@@ -1312,7 +1312,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="E14" s="1">
         <v>16</v>
@@ -1356,7 +1356,7 @@
         <v>7</v>
       </c>
       <c r="D15" s="1">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E15" s="1">
         <v>8</v>
@@ -1400,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="1">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="E16" s="1">
         <v>12</v>
@@ -1444,7 +1444,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="1">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E17" s="1">
         <v>20</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -784,7 +784,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1">
         <v>4</v>
@@ -796,16 +796,16 @@
         <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="1">
         <v>2</v>
@@ -828,7 +828,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="1">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1">
         <v>4</v>
@@ -840,16 +840,16 @@
         <v>0.6</v>
       </c>
       <c r="H3" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J3" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L3" s="1">
         <v>1.6</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E4" s="1">
         <v>12</v>
@@ -884,16 +884,16 @@
         <v>2</v>
       </c>
       <c r="H4" s="1">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="I4" s="1">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="J4" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K4" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L4" s="1">
         <v>4.0</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -1183,10 +1183,10 @@
         <v>252</v>
       </c>
       <c r="E11" s="1">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -1183,10 +1183,10 @@
         <v>252</v>
       </c>
       <c r="E11" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F11" s="1">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>

--- a/Assets/02_Resources/Data/MonsterData.xlsx
+++ b/Assets/02_Resources/Data/MonsterData.xlsx
@@ -1183,7 +1183,7 @@
         <v>252</v>
       </c>
       <c r="E11" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1">
         <v>4</v>
